--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487437_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487437_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0547</v>
+        <v>5.0782</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4186</v>
+        <v>4.6827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6361</v>
+        <v>0.3955</v>
       </c>
       <c r="G2" t="n">
         <v>6.1743</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.865</v>
+        <v>-0.8415</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7128</v>
+        <v>-0.4488</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1521</v>
+        <v>-0.3927</v>
       </c>
       <c r="V2" t="n">
         <v>0.3329</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.062</v>
+        <v>3.0793</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1545</v>
+        <v>1.7177</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9075</v>
+        <v>1.3616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5476</v>
+        <v>0.9403</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0419</v>
+        <v>1.3797</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5057</v>
+        <v>-0.4394</v>
       </c>
       <c r="J3" t="n">
-        <v>1.207</v>
+        <v>1.181</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1262</v>
+        <v>3.1421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0808</v>
+        <v>-1.9611</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6594</v>
+        <v>-0.2407</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0843</v>
+        <v>-1.7624</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4249</v>
+        <v>1.5217</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7102</v>
+        <v>-1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>0.414</v>
+        <v>-0.8216</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2962</v>
+        <v>-0.6684</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6083</v>
+        <v>3.0415</v>
       </c>
       <c r="W3" t="n">
-        <v>1.492</v>
+        <v>3.3169</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5525</v>
+        <v>2.3549</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3513</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2012</v>
+        <v>1.8483</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9403</v>
+        <v>3.2988</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3797</v>
+        <v>-1.2228</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4394</v>
+        <v>4.5217</v>
       </c>
       <c r="J4" t="n">
-        <v>1.181</v>
+        <v>2.5219</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1421</v>
+        <v>0.199</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9611</v>
+        <v>2.3229</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2407</v>
+        <v>0.777</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7624</v>
+        <v>-1.4218</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5217</v>
+        <v>2.1987</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.0168</v>
+        <v>-1.9439</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.188</v>
+        <v>-0.9404</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8288</v>
+        <v>-1.0035</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0415</v>
+        <v>0.6083</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3169</v>
+        <v>0.8837</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9618</v>
+        <v>1.6833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1402</v>
+        <v>0.4976</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8216</v>
+        <v>1.1858</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2988</v>
+        <v>0.5476</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2228</v>
+        <v>0.0419</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5217</v>
+        <v>0.5057</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5219</v>
+        <v>1.207</v>
       </c>
       <c r="K5" t="n">
-        <v>0.199</v>
+        <v>1.1262</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3229</v>
+        <v>0.0808</v>
       </c>
       <c r="M5" t="n">
-        <v>0.777</v>
+        <v>-0.6594</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4218</v>
+        <v>-1.0843</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1987</v>
+        <v>0.4249</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.3371</v>
+        <v>0.3316</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3068</v>
+        <v>-0.2429</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0302</v>
+        <v>0.5745</v>
       </c>
       <c r="V5" t="n">
         <v>0.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8837</v>
+        <v>1.492</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7237</v>
+        <v>-0.6703</v>
       </c>
       <c r="E6" t="n">
         <v>0.7178</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4415</v>
+        <v>-1.3881</v>
       </c>
       <c r="G6" t="n">
         <v>0.6491</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4684</v>
+        <v>-0.4149</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3496</v>
+        <v>-0.2961</v>
       </c>
       <c r="V6" t="n">
         <v>-1.492</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9596</v>
+        <v>-0.9061</v>
       </c>
       <c r="E7" t="n">
         <v>0.0043</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9638</v>
+        <v>-0.9104</v>
       </c>
       <c r="G7" t="n">
         <v>0.8043</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8007</v>
+        <v>-0.7472</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="V7" t="n">
         <v>-1.159</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8932</v>
+        <v>-1.5979</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7008</v>
+        <v>-2.3214</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1924</v>
+        <v>0.7235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1096</v>
+        <v>-1.3236</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5189</v>
+        <v>-3.6176</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4093</v>
+        <v>2.294</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6414</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0408</v>
+        <v>-1.6469</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6822</v>
+        <v>0.6515</v>
       </c>
       <c r="M8" t="n">
-        <v>0.751</v>
+        <v>-0.3281</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4781</v>
+        <v>-1.9707</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2729</v>
+        <v>1.6426</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3917</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5695</v>
+        <v>-1.0992</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>-0.584</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5101</v>
+        <v>-0.5152</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8249</v>
+        <v>1.2166</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1782</v>
+        <v>-1.8397</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6878</v>
+        <v>-0.7008</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5096000000000001</v>
+        <v>-1.1389</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3236</v>
+        <v>0.1096</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.6176</v>
+        <v>0.5189</v>
       </c>
       <c r="I9" t="n">
-        <v>2.294</v>
+        <v>-0.4093</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.6414</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6469</v>
+        <v>0.0408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6515</v>
+        <v>-0.6822</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3281</v>
+        <v>0.751</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9707</v>
+        <v>0.4781</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6426</v>
+        <v>0.2729</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6795</v>
+        <v>-0.5161</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9504</v>
+        <v>-0.0594</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.729</v>
+        <v>-0.4567</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2166</v>
+        <v>-1.8249</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3604</v>
+        <v>-2.2</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6831</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6773</v>
+        <v>-1.5169</v>
       </c>
       <c r="G10" t="n">
         <v>0.1558</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3411</v>
+        <v>-1.1807</v>
       </c>
       <c r="T10" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9847</v>
+        <v>-0.8243</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7199</v>
+        <v>-2.8887</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3013</v>
+        <v>-2.7107</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4186</v>
+        <v>-0.178</v>
       </c>
       <c r="G11" t="n">
         <v>-0.09669999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4482</v>
+        <v>-1.6169</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0306</v>
+        <v>-0.4399</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4176</v>
+        <v>-1.177</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.796</v>
+        <v>2.092999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4137</v>
+        <v>1.710699999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3823999999999999</v>
+        <v>0.3824000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>11.2595</v>
       </c>
       <c r="H12" t="n">
-        <v>2.390500000000001</v>
+        <v>2.3905</v>
       </c>
       <c r="I12" t="n">
         <v>8.869000000000002</v>
@@ -1375,7 +1375,7 @@
         <v>-0.8337000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.468299999999999</v>
+        <v>-8.468300000000001</v>
       </c>
       <c r="O12" t="n">
         <v>7.6344</v>
@@ -1390,10 +1390,10 @@
         <v>12.73</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.816099999999999</v>
+        <v>-9.518799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.487399999999999</v>
+        <v>-4.190399999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-5.3284</v>
@@ -1402,7 +1402,7 @@
         <v>1.331700000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.517499999999999</v>
+        <v>7.5175</v>
       </c>
       <c r="X12" t="n">
         <v>-6.1858</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4639</v>
+        <v>5.6999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3045</v>
+        <v>4.4069</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1594</v>
+        <v>1.2931</v>
       </c>
       <c r="G13" t="n">
         <v>1.7981</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1566</v>
+        <v>1.3926</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6869</v>
+        <v>0.7893</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4696</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.5507</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7672</v>
+        <v>4.7183</v>
       </c>
       <c r="E14" t="n">
-        <v>6.137</v>
+        <v>6.0347</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3698</v>
+        <v>-1.3164</v>
       </c>
       <c r="G14" t="n">
         <v>1.5994</v>
@@ -1546,13 +1546,13 @@
         <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6136</v>
+        <v>1.5647</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9839</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6297</v>
+        <v>0.6831</v>
       </c>
       <c r="V14" t="n">
         <v>3.3169</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0563</v>
+        <v>2.0935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6106</v>
+        <v>1.0755</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4457</v>
+        <v>1.018</v>
       </c>
       <c r="G15" t="n">
         <v>1.1363</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1953</v>
+        <v>2.2326</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9119</v>
+        <v>1.3768</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2834</v>
+        <v>0.8557</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8837</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3242</v>
+        <v>1.1051</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0381</v>
+        <v>0.8581</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2862</v>
+        <v>0.247</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7972</v>
+        <v>0.346</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3879</v>
+        <v>2.9077</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4093</v>
+        <v>-2.5617</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.9491</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0204</v>
+        <v>3.991</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6822</v>
+        <v>-2.0419</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1354</v>
+        <v>-1.6031</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4083</v>
+        <v>-1.0833</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2729</v>
+        <v>-0.5198</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9256</v>
+        <v>0.8006</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6999</v>
+        <v>-0.1118</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2257</v>
+        <v>0.9124</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2154</v>
+        <v>0.0126</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1653</v>
+        <v>-0.1666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3807</v>
+        <v>0.1792</v>
       </c>
       <c r="G17" t="n">
-        <v>0.346</v>
+        <v>-0.7972</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9077</v>
+        <v>-0.3879</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5617</v>
+        <v>-0.4093</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9491</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>3.991</v>
+        <v>0.0204</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0419</v>
+        <v>-0.6822</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6031</v>
+        <v>-0.1354</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0833</v>
+        <v>-0.4083</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5198</v>
+        <v>0.2729</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0891</v>
+        <v>0.614</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1351</v>
+        <v>0.4952</v>
       </c>
       <c r="U17" t="n">
-        <v>1.046</v>
+        <v>0.1188</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2132</v>
+        <v>-1.1244</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.879</v>
+        <v>0.7088</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3342</v>
+        <v>-1.8333</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0674</v>
+        <v>0.4489</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4352</v>
+        <v>0.7166</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6322</v>
+        <v>-0.2677</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3236</v>
+        <v>1.327</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0408</v>
+        <v>1.327</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3645</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7437</v>
+        <v>-0.8781</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.476</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>-0.2677</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3917</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4624</v>
+        <v>0.4474</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4446</v>
+        <v>0.3611</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0863</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.227</v>
+        <v>-1.1957</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6256</v>
+        <v>-1.7279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3986</v>
+        <v>0.5322</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6203</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3138</v>
+        <v>0.3451</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3611</v>
+        <v>0.2588</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0473</v>
+        <v>0.0863</v>
       </c>
       <c r="V19" t="n">
         <v>0.2754</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2581</v>
+        <v>-1.3995</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7088</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9669</v>
+        <v>-0.8355</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4489</v>
+        <v>-3.1327</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7166</v>
+        <v>-0.0248</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2677</v>
+        <v>-3.1079</v>
       </c>
       <c r="J20" t="n">
-        <v>1.327</v>
+        <v>-1.237</v>
       </c>
       <c r="K20" t="n">
-        <v>1.327</v>
+        <v>2.0126</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-3.2495</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8781</v>
+        <v>-1.8957</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-2.0373</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2677</v>
+        <v>0.1416</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7834</v>
+        <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3138</v>
+        <v>0.7159</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3611</v>
+        <v>0.3976</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0473</v>
+        <v>0.3183</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8249</v>
+        <v>-0.9412</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7775</v>
+        <v>-1.4935</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0757</v>
+        <v>-1.186</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7018</v>
+        <v>-0.3075</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1327</v>
+        <v>-2.0674</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0248</v>
+        <v>-0.4352</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1079</v>
+        <v>-1.6322</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.237</v>
+        <v>-1.3236</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0126</v>
+        <v>0.0408</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2495</v>
+        <v>-1.3645</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8957</v>
+        <v>-0.7437</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0373</v>
+        <v>-0.476</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1416</v>
+        <v>-0.2677</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3379</v>
+        <v>0.1822</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1141</v>
+        <v>0.1376</v>
       </c>
       <c r="U21" t="n">
-        <v>0.452</v>
+        <v>0.0446</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0835</v>
+        <v>-3.6382</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0161</v>
+        <v>-3.8114</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0674</v>
+        <v>0.1732</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8841</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1716</v>
+        <v>0.6168</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0723</v>
+        <v>0.1323</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2439</v>
+        <v>0.4845</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0637</v>
+        <v>-6.5742</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4196</v>
+        <v>-6.0103</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6441</v>
+        <v>-0.5639</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0866</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4146</v>
+        <v>0.9041</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2005</v>
+        <v>0.6099</v>
       </c>
       <c r="U23" t="n">
-        <v>0.214</v>
+        <v>0.2942</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.796000000000001</v>
+        <v>-1.7961</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3822999999999999</v>
+        <v>-0.3821999999999992</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4136</v>
+        <v>-1.413899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-11.2596</v>
@@ -2299,10 +2299,10 @@
         <v>-8.869</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8338999999999999</v>
+        <v>0.8339000000000008</v>
       </c>
       <c r="K24" t="n">
-        <v>8.468099999999998</v>
+        <v>8.4681</v>
       </c>
       <c r="L24" t="n">
         <v>-7.6342</v>
@@ -2326,19 +2326,19 @@
         <v>13.7094</v>
       </c>
       <c r="S24" t="n">
-        <v>9.816099999999999</v>
+        <v>9.815999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>5.3284</v>
+        <v>5.328399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>4.487500000000001</v>
+        <v>4.4875</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3317</v>
       </c>
       <c r="W24" t="n">
-        <v>6.185700000000001</v>
+        <v>6.1857</v>
       </c>
       <c r="X24" t="n">
         <v>-7.5174</v>
